--- a/public/sap-reporting/expansion-150-downloads/EXT-SD11-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-SD11-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R2b32c60724394c38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R983fea8fcd5447df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rc62527597a0d4059"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R2ebfdf3fda414568"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R164b71de58bb4ed5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rc50053f9c6b441e2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1458,7 +1458,7 @@
         <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="63" customHeight="1">
+    <x:row r="15" ht="80" customHeight="1">
       <x:c r="A15" s="8" t="str">
         <x:v>14</x:v>
       </x:c>
@@ -1466,7 +1466,7 @@
         <x:v>Price Unit</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>raw_decimal</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
         <x:v>Số đơn vị làm mẫu số của đơn giá</x:v>
@@ -1475,7 +1475,7 @@
         <x:v>SAVA_PROPOSED / chưa xác minh</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
+        <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="80" customHeight="1">
